--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -603,7 +603,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aspida 12.25%-14Nov28</t>
+          <t>Aspida-0%-14Nov28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -623,7 +623,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
@@ -683,7 +683,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Axa 65%-18Aug27</t>
+          <t>AXA-15%-18Aug27</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,6 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,7 +490,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Issuer</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -506,104 +505,99 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>CAP</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Part.</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Floor Type</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Strike</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Last Reset</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Days to Maturity</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Reset Freq</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>Next Reset</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>Days to Reset</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>Initial ($000)</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>Realized ($000)</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>Proj Value @ Reset ($000)</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>Proj $ Gain @ Reset ($000)</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-      <c r="U3" s="1" t="inlineStr">
-        <is>
-          <t>Issuer</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="inlineStr">
-        <is>
-          <t>Index</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aspida-0%-14Nov28</t>
+          <t>Aspida</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -612,78 +606,73 @@
       <c r="C4" s="2" t="n">
         <v>0.1225</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>0.1225</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Absolute</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="I4" s="3" t="n">
         <v>6271.19</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>45247</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>45974</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>47071</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>884</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>46339</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>152</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="R4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="5" t="n">
+      <c r="S4" s="5" t="n">
         <v>112.25</v>
       </c>
-      <c r="S4" s="5" t="n">
+      <c r="T4" s="5" t="n">
         <v>12.25</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Non-Qual</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Aspida</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SPX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AXA-15%-18Aug27</t>
+          <t>AXA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -692,71 +681,66 @@
       <c r="C5" s="2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>-0.15</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="I5" s="3" t="n">
         <v>9487.18</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>44426</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>44426</v>
       </c>
       <c r="K5" s="4" t="n">
+        <v>44426</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>46617</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>430</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>6-Year</t>
         </is>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>46617</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>430</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="5" t="n">
+      <c r="S5" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="T5" s="5" t="n">
         <v>-7.000000000000001</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Non-Qual</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>AXA</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SPX</t>
         </is>
       </c>
     </row>
@@ -769,32 +753,31 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="8" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="9" t="n"/>
-      <c r="L6" s="6" t="n"/>
+      <c r="L6" s="9" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="9" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="10" t="n">
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="R6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="S6" s="10" t="n">
         <v>205.25</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="T6" s="10" t="n">
         <v>5.249999999999999</v>
       </c>
-      <c r="T6" s="6" t="n"/>
       <c r="U6" s="6" t="n"/>
-      <c r="V6" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,9 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,121 +486,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Blue=inputs  Black=formula | Floor 0% = floor; negative Hard = buffer; negative Soft = barrier | $ columns in $000s</t>
+          <t>Floor Type: Protected (0% floor), Hard (buffer — absorbs first |floor|), Soft (barrier — full loss if breached) | CAP 9.99 = uncapped | $ columns in $000s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Index Gain %</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Proj Gain @ Reset</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Part.</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Floor Type</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Strike</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Last Reset</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>Days to Maturity</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Reset Freq</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Next Reset</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Days to Reset</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Initial ($000)</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Realized ($000)</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>Proj Value @ Reset ($000)</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>Proj $ Gain @ Reset ($000)</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Index Gain %</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Proj Gain @ Reset</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>CAP</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Part.</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Floor</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Floor Type</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Strike</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Last Reset</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Maturity</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>Days to Maturity</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Reset Freq</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>Next Reset</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>Days to Reset</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>Initial ($000)</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>Realized ($000)</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>Proj Value @ Reset ($000)</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
-        <is>
-          <t>Proj $ Gain @ Reset ($000)</t>
-        </is>
-      </c>
-      <c r="U3" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
+      <c r="W3" s="1" t="inlineStr">
+        <is>
+          <t>NDX_Strike</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>RUT_Strike</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aspida</t>
+          <t>ASPIDA-0%-14Nov28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -606,73 +624,80 @@
       <c r="C4" s="2" t="n">
         <v>0.1225</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
+      <c r="D4" s="2" t="n">
+        <v>0.1225</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.1225</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Absolute</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Protected</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>6271.19</v>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>45247</v>
+      </c>
       <c r="J4" s="4" t="n">
-        <v>45247</v>
+        <v>45974</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>45974</v>
-      </c>
-      <c r="L4" s="4" t="n">
         <v>47071</v>
       </c>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
         <v>884</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>46339</v>
       </c>
-      <c r="P4" t="n">
+      <c r="O4" t="n">
         <v>152</v>
       </c>
+      <c r="P4" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="Q4" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>0</v>
+        <v>112.25</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>112.25</v>
-      </c>
-      <c r="T4" s="5" t="n">
         <v>12.25</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Non-Qual</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Non-Qual</t>
-        </is>
-      </c>
+          <t>ASPIDA</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AXA</t>
+          <t>AXA-15%-18Aug27</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -681,68 +706,75 @@
       <c r="C5" s="2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
+      <c r="D5" s="2" t="n">
+        <v>0.65</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="n">
         <v>-0.15</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>9487.18</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>44426</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>44426</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>44426</v>
-      </c>
-      <c r="L5" s="4" t="n">
         <v>46617</v>
       </c>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
         <v>430</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>6-Year</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Inception</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>46617</v>
       </c>
-      <c r="P5" t="n">
+      <c r="O5" t="n">
         <v>430</v>
       </c>
+      <c r="P5" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="Q5" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="T5" s="5" t="n">
         <v>-7.000000000000001</v>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Non-Qual</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Non-Qual</t>
-        </is>
-      </c>
+          <t>AXA</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -752,32 +784,35 @@
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="8" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="9" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
+      <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="10" t="n">
+        <v>200</v>
+      </c>
       <c r="Q6" s="10" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>0</v>
+        <v>205.25</v>
       </c>
       <c r="S6" s="10" t="n">
-        <v>205.25</v>
-      </c>
-      <c r="T6" s="10" t="n">
         <v>5.249999999999999</v>
       </c>
+      <c r="T6" s="6" t="n"/>
       <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -790,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -801,7 +836,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>iHaveAnnuities — Tracker template</t>
+          <t>iHaveAnnuities — Tracker template (schema v1.0)</t>
         </is>
       </c>
     </row>
@@ -818,7 +853,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>are read by the app; FORMULA columns are recomputed on import.</t>
+          <t>are read by the app; DERIVED columns are recomputed on import.</t>
         </is>
       </c>
     </row>
@@ -850,12 +885,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Free-text name, e.g. 'AIG 11%-17Jan29'</t>
+          <t>Never edited; rewritten on export as {ISSUER}-{|floor|%}-{ddMMMyy}</t>
         </is>
       </c>
     </row>
@@ -867,7 +902,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -884,7 +919,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +941,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>e.g. 11.25%  — or the word 'Uncapped'</t>
+          <t>Fraction, e.g. 0.1125 = 11.25%. 9.99 = uncapped sentinel</t>
         </is>
       </c>
     </row>
@@ -923,7 +958,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Participation rate, e.g. 100% (or 92.25%, 105%)</t>
+          <t>Participation rate, e.g. 1.00 = 100% (or 0.9225, 1.05)</t>
         </is>
       </c>
     </row>
@@ -940,7 +975,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;= 0. 0% = floor; negative = buffer/barrier amount</t>
+          <t>&lt;= 0. 0 = Protected; negative = buffer (Hard) / barrier (Soft) amount</t>
         </is>
       </c>
     </row>
@@ -957,7 +992,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'Hard' (floor/buffer) or 'Soft' (barrier)</t>
+          <t>'Protected' (floor=0), 'Hard' (buffer), or 'Soft' (barrier)</t>
         </is>
       </c>
     </row>
@@ -974,7 +1009,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Index level at open / last reset</t>
+          <t>Index level at open / last reset (SPX strike for worst-of)</t>
         </is>
       </c>
     </row>
@@ -998,41 +1033,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reset Freq</t>
+          <t>Days to Maturity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Annual, Monthly, 4-Year, 5-Year, or 6-Year</t>
+          <t>Recomputed from Maturity</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Next Reset</t>
+          <t>Reset Freq</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Recomputed from Reset Freq</t>
+          <t>'Inception' (point-to-point), 'Annual', or 'Monthly'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Initial ($000)</t>
+          <t>Next Reset</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,48 +1077,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Principal in thousands, e.g. 100 = $100,000</t>
+          <t>Date of next reset</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Realized ($000)</t>
+          <t>Days to Reset</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gains locked at prior resets, in $000</t>
+          <t>Recomputed from Next Reset</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Proj Value / Proj $ Gain</t>
+          <t>Initial ($000)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Recomputed</t>
+          <t>Principal in thousands, e.g. 100 = $100,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Realized ($000)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1093,41 +1128,92 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Non-Qual, IRA, or ROTH</t>
+          <t>Cumulative coupons/income to date, in $000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Issuer</t>
+          <t>Proj Value / Proj $ Gain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Carrier, e.g. AIG</t>
+          <t>Recomputed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'Non-Qual', 'IRA', or 'ROTH'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Canonical short name, uppercase (e.g. AIG, ASPIDA, NATBANK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SPX, NDX, RUT, or 'worst-of SPX/NDX/RUT'</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>'^GSPC', '^NDX', '^RUT', or 'SPX/NDX/RUT' for worst-of</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NDX_Strike / RUT_Strike</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Worst-of notes only: NDX &amp; RUT levels at open</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -479,7 +479,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ZUCKER ANNUITY TRACKER — Updated June 14, 2026 (prices: SPX 7,400.00  NDX 29,600  RUT 2,950.00)</t>
+          <t>ZUCKER ANNUITY TRACKER — Updated 14-Jun-26 (prices: SPX 7,400.00  NDX 29,600  RUT 2,950.00)</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -72,15 +72,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -498,107 +498,107 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Floor Type</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Proj Value @ Reset ($000)</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Proj $ Gain @ Reset ($000)</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Proj Gain @ Reset</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
           <t>Index Gain %</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Proj Gain @ Reset</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>CAP</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Part.</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Floor Type</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Strike</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Next Reset</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Days to Reset</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Days to Maturity</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>Reset Freq</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>Last Reset</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Maturity</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Days to Maturity</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>Reset Freq</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Next Reset</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>Days to Reset</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>Initial ($000)</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>Realized ($000)</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>Proj Value @ Reset ($000)</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>Proj $ Gain @ Reset ($000)</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="U3" s="1" t="inlineStr">
-        <is>
-          <t>Issuer</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="inlineStr">
-        <is>
-          <t>Index</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
@@ -618,81 +618,81 @@
           <t>ASPIDA-0%-14Nov28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ASPIDA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Non-Qual</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Protected</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>0.18</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.1225</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Protected</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
+      <c r="M4" s="4" t="n">
         <v>6271.19</v>
       </c>
-      <c r="I4" s="4" t="n">
-        <v>45247</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>45974</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>47071</v>
-      </c>
-      <c r="L4" t="n">
-        <v>884</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>46339</v>
       </c>
       <c r="O4" t="n">
         <v>152</v>
       </c>
       <c r="P4" s="5" t="n">
+        <v>47071</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>884</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>45247</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>45974</v>
+      </c>
+      <c r="U4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="V4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="5" t="n">
-        <v>112.25</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Non-Qual</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>ASPIDA</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -700,81 +700,81 @@
           <t>AXA-15%-18Aug27</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AXA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Non-Qual</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-7.000000000000001</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>-0.22</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="L5" s="3" t="n">
         <v>-0.15</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="M5" s="4" t="n">
         <v>9487.18</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>44426</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>44426</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>46617</v>
-      </c>
-      <c r="L5" t="n">
-        <v>430</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Inception</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>46617</v>
       </c>
       <c r="O5" t="n">
         <v>430</v>
       </c>
       <c r="P5" s="5" t="n">
+        <v>46617</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>430</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Inception</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>44426</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>44426</v>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>-7.000000000000001</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Non-Qual</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>AXA</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>^GSPC</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="n"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -782,37 +782,37 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="n">
+        <v>205.25</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>5.249999999999999</v>
+      </c>
       <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="9" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="10" t="n"/>
       <c r="O6" s="6" t="n"/>
-      <c r="P6" s="10" t="n">
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="V6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="10" t="n">
-        <v>205.25</v>
-      </c>
-      <c r="S6" s="10" t="n">
-        <v>5.249999999999999</v>
-      </c>
-      <c r="T6" s="6" t="n"/>
-      <c r="U6" s="6" t="n"/>
-      <c r="V6" s="6" t="n"/>
-      <c r="W6" s="8" t="n"/>
-      <c r="X6" s="8" t="n"/>
+      <c r="W6" s="9" t="n"/>
+      <c r="X6" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -836,7 +836,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>iHaveAnnuities — Tracker template (schema v1.0)</t>
+          <t>iHaveAnnuities — Tracker template (schema v1.1)</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -74,13 +74,13 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -518,87 +518,87 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
+          <t>Initial ($000)</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Realized ($000)</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
           <t>Proj Value @ Reset ($000)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Proj $ Gain @ Reset ($000)</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Proj Gain @ Reset</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Index Gain %</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>Next Reset</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Days to Reset</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Days to Maturity</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>CAP</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>Part.</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>Strike</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Next Reset</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>Days to Reset</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>Maturity</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>Days to Maturity</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>Reset Freq</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>Last Reset</t>
-        </is>
-      </c>
-      <c r="U3" s="1" t="inlineStr">
-        <is>
-          <t>Initial ($000)</t>
-        </is>
-      </c>
-      <c r="V3" s="1" t="inlineStr">
-        <is>
-          <t>Realized ($000)</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
@@ -639,60 +639,60 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>112.25</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>12.25</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.18</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0.1225</v>
       </c>
       <c r="K4" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>46339</v>
+      </c>
+      <c r="M4" t="n">
+        <v>152</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>47071</v>
+      </c>
+      <c r="O4" t="n">
+        <v>884</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="S4" s="5" t="n">
         <v>6271.19</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>46339</v>
-      </c>
-      <c r="O4" t="n">
-        <v>152</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>47071</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>884</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="S4" s="5" t="n">
+      <c r="U4" s="4" t="n">
         <v>45247</v>
       </c>
-      <c r="T4" s="5" t="n">
+      <c r="V4" s="4" t="n">
         <v>45974</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -721,60 +721,60 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>-7.000000000000001</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>-0.22</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>9487.18</v>
-      </c>
-      <c r="N5" s="5" t="n">
+      <c r="L5" s="4" t="n">
+        <v>46617</v>
+      </c>
+      <c r="M5" t="n">
+        <v>430</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>46617</v>
       </c>
       <c r="O5" t="n">
         <v>430</v>
       </c>
-      <c r="P5" s="5" t="n">
-        <v>46617</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>430</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P5" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>9487.18</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Inception</t>
         </is>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="U5" s="4" t="n">
         <v>44426</v>
       </c>
-      <c r="T5" s="5" t="n">
+      <c r="V5" s="4" t="n">
         <v>44426</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -787,32 +787,32 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <v>205.25</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="I6" s="7" t="n">
         <v>5.249999999999999</v>
       </c>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="10" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="9" t="n"/>
       <c r="O6" s="6" t="n"/>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
       <c r="S6" s="10" t="n"/>
-      <c r="T6" s="10" t="n"/>
-      <c r="U6" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="V6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="9" t="n"/>
-      <c r="X6" s="9" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -836,7 +836,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>iHaveAnnuities — Tracker template (schema v1.1)</t>
+          <t>iHaveAnnuities — Tracker template (schema v1.2)</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Floor Type: Protected (0% floor), Hard (buffer — absorbs first |floor|), Soft (barrier — full loss if breached) | CAP 9.99 = uncapped | $ columns in $000s</t>
+          <t>Floor Type: Protected (0% floor), Hard (buffer — absorbs first |floor|), Soft (barrier — full loss if breached), Floor (max loss — lose only down to the floor) | CAP 9.99 = uncapped | $ columns in $000s</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;= 0. 0 = Protected; negative = buffer (Hard) / barrier (Soft) amount</t>
+          <t>&lt;= 0. 0 = Protected; negative = buffer (Hard) / barrier (Soft) / max-loss (Floor) amount</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'Protected' (floor=0), 'Hard' (buffer), or 'Soft' (barrier)</t>
+          <t>'Protected' (floor=0), 'Hard' (buffer), 'Soft' (barrier), or 'Floor' (max loss)</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Floor Type: Protected (0% floor), Hard (buffer — absorbs first |floor|), Soft (barrier — full loss if breached), Floor (max loss — lose only down to the floor) | CAP 9.99 = uncapped | $ columns in $000s</t>
+          <t>Floor Type: Floor (max loss — lose only down to the floor; 0% floor = no loss), Hard-buffer (absorbs first |floor|, lose beyond), Soft-buffer (barrier — full loss if breached) | CAP 9.99 = uncapped | $ columns in $000s</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Protected</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Hard-buffer</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;= 0. 0 = Protected; negative = buffer (Hard) / barrier (Soft) / max-loss (Floor) amount</t>
+          <t>&lt;= 0. 0 = no loss (a Floor at 0%); negative = the protection level</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'Protected' (floor=0), 'Hard' (buffer), 'Soft' (barrier), or 'Floor' (max loss)</t>
+          <t>'Floor' (max loss), 'Hard-buffer' (absorbs first |floor|), or 'Soft-buffer' (barrier)</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Floor Type: Floor (max loss — lose only down to the floor; 0% floor = no loss), Hard-buffer (absorbs first |floor|, lose beyond), Soft-buffer (barrier — full loss if breached) | CAP 9.99 = uncapped | $ columns in $000s</t>
+          <t>Floor Type: Floor (max loss — lose only down to the floor; 0% floor = no loss), Hard (buffer — absorbs first |floor|, lose beyond), Soft (barrier — full loss if breached) | CAP 9.99 = uncapped | $ columns in $000s</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hard-buffer</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'Floor' (max loss), 'Hard-buffer' (absorbs first |floor|), or 'Soft-buffer' (barrier)</t>
+          <t>'Floor' (max loss), 'Hard' (buffer — absorbs first |floor|), or 'Soft' (barrier)</t>
         </is>
       </c>
     </row>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,7 @@
     <col width="15" customWidth="1" min="22" max="22"/>
     <col width="15" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -593,7 +594,7 @@
       </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="V3" s="1" t="inlineStr">
@@ -609,6 +610,11 @@
       <c r="X3" s="1" t="inlineStr">
         <is>
           <t>RUT_Strike</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>Inception</t>
         </is>
       </c>
     </row>
@@ -693,6 +699,7 @@
       </c>
       <c r="W4" s="5" t="n"/>
       <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -764,7 +771,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Inception</t>
+          <t>Once</t>
         </is>
       </c>
       <c r="U5" s="4" t="n">
@@ -775,6 +782,7 @@
       </c>
       <c r="W5" s="5" t="n"/>
       <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -813,6 +821,7 @@
       <c r="V6" s="9" t="n"/>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -825,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1016,7 +1025,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Open / Last Reset / Maturity</t>
+          <t>Start Date / Last Reset / Maturity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1033,41 +1042,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Days to Maturity</t>
+          <t>Inception</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Recomputed from Maturity</t>
+          <t>Optional original investment date for a rolled contract; drives Yield/CAGR (blank = use Start Date)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Reset Freq</t>
+          <t>Days to Maturity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'Inception' (point-to-point), 'Annual', or 'Monthly'</t>
+          <t>Recomputed from Maturity</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Next Reset</t>
+          <t>Reset Freq</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1077,48 +1086,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date of next reset</t>
+          <t>'Once' (point-to-point), 'Annual', or 'Monthly'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Days to Reset</t>
+          <t>Next Reset</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Recomputed from Next Reset</t>
+          <t>Date of next reset</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Initial ($000)</t>
+          <t>Days to Reset</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Principal in thousands, e.g. 100 = $100,000</t>
+          <t>Recomputed from Next Reset</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Realized ($000)</t>
+          <t>Initial ($000)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1128,48 +1137,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cumulative coupons/income to date, in $000</t>
+          <t>Principal in thousands, e.g. 100 = $100,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Proj Value / Proj $ Gain</t>
+          <t>Realized ($000)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Recomputed</t>
+          <t>Cumulative coupons/income to date, in $000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Proj Value / Proj $ Gain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'Non-Qual', 'IRA', or 'ROTH'</t>
+          <t>Recomputed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Issuer</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1179,14 +1188,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Canonical short name, uppercase (e.g. AIG, ASPIDA, NATBANK)</t>
+          <t>'Non-Qual', 'IRA', or 'ROTH'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Issuer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1196,22 +1205,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'^GSPC', '^NDX', '^RUT', or 'SPX/NDX/RUT' for worst-of</t>
+          <t>Canonical short name, uppercase (e.g. AIG, ASPIDA, NATBANK)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>'^GSPC', '^NDX', '^RUT', or 'SPX/NDX/RUT' for worst-of</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>NDX_Strike / RUT_Strike</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Worst-of notes only: NDX &amp; RUT levels at open</t>
         </is>

--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>112.25</v>
+        <v>11.225</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.25</v>
+        <v>1.225</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0.1225</v>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>93</v>
+        <v>9.299999999999999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-7.000000000000001</v>
+        <v>-0.7000000000000001</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -795,16 +795,16 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="7" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>205.25</v>
+        <v>20.525</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>5.249999999999999</v>
+        <v>0.525</v>
       </c>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Principal in thousands, e.g. 100 = $100,000</t>
+          <t>Principal in thousands, e.g. 10 = $10,000</t>
         </is>
       </c>
     </row>
